--- a/Data/Pilot Data--Excel/CS424 Sharma Small Data Sample 1.xlsx
+++ b/Data/Pilot Data--Excel/CS424 Sharma Small Data Sample 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\ssharma\CS424_Fall2016_Project\Data\Pilot Data--Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CB1B8F0-6E68-43D6-9948-F05FBB3E93B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D1DD1F-B3BE-4178-8BD6-0BF325A48A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="27">
-  <si>
-    <t>Observation ID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="43">
   <si>
     <t>Date</t>
   </si>
@@ -39,9 +36,6 @@
     <t>Route</t>
   </si>
   <si>
-    <t>Stop</t>
-  </si>
-  <si>
     <t>Direction</t>
   </si>
   <si>
@@ -106,14 +100,69 @@
   </si>
   <si>
     <t>On time; longer-than-expected following gap</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Stop-Street</t>
+  </si>
+  <si>
+    <t>Stop-CTA ID</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>900 W Taylor</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>Lunt and Sheridan</t>
+  </si>
+  <si>
+    <t>1 minute early; bus arrived shortly after another bus</t>
+  </si>
+  <si>
+    <t>1 minute early; bus closely followed previous bus; possible bunching</t>
+  </si>
+  <si>
+    <t>1 minute early; three buses arrived within approximately 4 minutes</t>
+  </si>
+  <si>
+    <t>1 minute early; large gap after previous group of buses; possible bunching followed by service gap</t>
+  </si>
+  <si>
+    <t>On time; approximately 20-minute gap after three closely spaced buses</t>
+  </si>
+  <si>
+    <t>1 minute late; first observed morning bus</t>
+  </si>
+  <si>
+    <t>1 minute late; approximately 30-minute spacing</t>
+  </si>
+  <si>
+    <t>On time; approximately 30-minute spacing</t>
+  </si>
+  <si>
+    <t>On time; next bus predicted approximately one hour later</t>
+  </si>
+  <si>
+    <t>On time; approximately one-hour gap from previous bus</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="h:mm;@"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="h:mm;@"/>
+    <numFmt numFmtId="166" formatCode="m/d/yy;@"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -154,10 +203,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -438,406 +487,881 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="44.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="43" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="55.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="43" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="85.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" s="4">
+        <v>46293</v>
+      </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>147</v>
       </c>
       <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2">
+        <v>1033</v>
+      </c>
+      <c r="G2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" s="3">
+        <v>0.36249999999999999</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="J2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="4">
-        <v>0.36249999999999999</v>
-      </c>
-      <c r="H2" s="4">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="I2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2">
+      <c r="K2">
         <v>12</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>11</v>
       </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
+      <c r="B3" s="4">
+        <v>46293</v>
+      </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>147</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3">
+        <v>1033</v>
+      </c>
+      <c r="G3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="H3" s="3">
         <v>0.37013888888888891</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="3">
         <v>0.37083333333333335</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>14</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>10</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>9</v>
       </c>
-      <c r="L3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
+      <c r="B4" s="4">
+        <v>46293</v>
+      </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D4">
         <v>147</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>1033</v>
+      </c>
+      <c r="G4" t="s">
         <v>14</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="4">
+      <c r="H4" s="3">
         <v>0.37708333333333333</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="3">
         <v>0.37777777777777777</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>10</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>12</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>13</v>
       </c>
-      <c r="L4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
+      <c r="B5" s="4">
+        <v>46293</v>
+      </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>147</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5">
+        <v>1033</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="4">
+      <c r="H5" s="3">
         <v>0.38611111111111113</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="3">
         <v>0.38680555555555557</v>
       </c>
-      <c r="I5">
+      <c r="J5">
         <v>13</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>9</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>8</v>
       </c>
-      <c r="L5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" s="4">
+        <v>46293</v>
+      </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D6">
         <v>147</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>1033</v>
+      </c>
+      <c r="G6" t="s">
         <v>14</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" s="3">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="J6">
+        <v>8</v>
+      </c>
+      <c r="K6">
+        <v>15</v>
+      </c>
+      <c r="L6">
         <v>16</v>
       </c>
-      <c r="G6" s="4">
-        <v>0.3923611111111111</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0.3923611111111111</v>
-      </c>
-      <c r="I6">
-        <v>8</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>16</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7" s="4">
+        <v>46288</v>
+      </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D7">
         <v>22</v>
       </c>
       <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7">
+        <v>1956</v>
+      </c>
+      <c r="G7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="H7" s="3">
         <v>0.73888888888888893</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="3">
         <v>0.73958333333333337</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7">
+        <v>8</v>
+      </c>
+      <c r="L7">
+        <v>7</v>
+      </c>
+      <c r="M7" t="s">
         <v>18</v>
       </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>7</v>
-      </c>
-      <c r="L7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
+      <c r="B8" s="4">
+        <v>46288</v>
+      </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D8">
         <v>22</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8">
+        <v>1956</v>
+      </c>
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="4">
+      <c r="H8" s="3">
         <v>0.74444444444444446</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="3">
         <v>0.74513888888888891</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>8</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>9</v>
       </c>
-      <c r="K8">
+      <c r="L8">
         <v>2</v>
       </c>
-      <c r="L8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" s="4">
+        <v>46288</v>
+      </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>22</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9">
+        <v>1956</v>
+      </c>
+      <c r="G9" t="s">
         <v>15</v>
       </c>
-      <c r="F9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="H9" s="3">
         <v>0.74652777777777779</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="3">
         <v>0.74652777777777779</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>2</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>11</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>9</v>
       </c>
-      <c r="L9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" s="4">
+        <v>46288</v>
+      </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D10">
         <v>22</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>1956</v>
+      </c>
+      <c r="G10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10" s="4">
+      <c r="H10" s="3">
         <v>0.75277777777777777</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="3">
         <v>0.75416666666666665</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>11</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>8</v>
       </c>
-      <c r="K10">
+      <c r="L10">
         <v>12</v>
       </c>
-      <c r="L10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11" s="4">
+        <v>46288</v>
+      </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11">
         <v>22</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>1956</v>
+      </c>
+      <c r="G11" t="s">
         <v>15</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" s="3">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="J11">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+      <c r="L11">
+        <v>14</v>
+      </c>
+      <c r="M11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46294</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12">
+        <v>157</v>
+      </c>
+      <c r="E12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12">
+        <v>6700</v>
+      </c>
+      <c r="G12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0.50555555555555554</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0.50486111111111109</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12">
+        <v>15</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46294</v>
+      </c>
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13">
+        <v>157</v>
+      </c>
+      <c r="E13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13">
+        <v>6700</v>
+      </c>
+      <c r="G13" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.50694444444444442</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.50624999999999998</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13">
+        <v>14</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46294</v>
+      </c>
+      <c r="C14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <v>157</v>
+      </c>
+      <c r="E14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14">
+        <v>6700</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0.5083333333333333</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0.50763888888888886</v>
+      </c>
+      <c r="J14">
+        <v>2</v>
+      </c>
+      <c r="K14">
+        <v>13</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46294</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15">
+        <v>157</v>
+      </c>
+      <c r="E15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15">
+        <v>6700</v>
+      </c>
+      <c r="G15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0.50972222222222219</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0.50902777777777775</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>12</v>
+      </c>
+      <c r="L15">
+        <v>20</v>
+      </c>
+      <c r="M15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46294</v>
+      </c>
+      <c r="C16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16">
+        <v>157</v>
+      </c>
+      <c r="E16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16">
+        <v>6700</v>
+      </c>
+      <c r="G16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0.5229166666666667</v>
+      </c>
+      <c r="J16">
+        <v>20</v>
+      </c>
+      <c r="K16">
+        <v>15</v>
+      </c>
+      <c r="L16" t="s">
+        <v>16</v>
+      </c>
+      <c r="M16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46296</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17">
+        <v>12060</v>
+      </c>
+      <c r="G17" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="3">
+        <v>0.20972222222222223</v>
+      </c>
+      <c r="I17" s="3">
+        <v>0.21041666666666667</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17">
+        <v>30</v>
+      </c>
+      <c r="L17">
+        <v>29</v>
+      </c>
+      <c r="M17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="G11" s="4">
-        <v>0.76249999999999996</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.76249999999999996</v>
-      </c>
-      <c r="I11">
-        <v>12</v>
-      </c>
-      <c r="J11">
-        <v>10</v>
-      </c>
-      <c r="K11">
-        <v>14</v>
-      </c>
-      <c r="L11" t="s">
-        <v>26</v>
+      <c r="B18" s="4">
+        <v>46296</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18">
+        <v>96</v>
+      </c>
+      <c r="E18" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18">
+        <v>12060</v>
+      </c>
+      <c r="G18" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0.23055555555555557</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0.23125000000000001</v>
+      </c>
+      <c r="J18">
+        <v>30</v>
+      </c>
+      <c r="K18">
+        <v>30</v>
+      </c>
+      <c r="L18">
+        <v>31</v>
+      </c>
+      <c r="M18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46296</v>
+      </c>
+      <c r="C19" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19">
+        <v>96</v>
+      </c>
+      <c r="E19" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19">
+        <v>12060</v>
+      </c>
+      <c r="G19" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.25208333333333333</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0.25208333333333333</v>
+      </c>
+      <c r="J19">
+        <v>30</v>
+      </c>
+      <c r="K19">
+        <v>30</v>
+      </c>
+      <c r="L19">
+        <v>29</v>
+      </c>
+      <c r="M19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46296</v>
+      </c>
+      <c r="C20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20">
+        <v>96</v>
+      </c>
+      <c r="E20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20">
+        <v>12060</v>
+      </c>
+      <c r="G20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0.2722222222222222</v>
+      </c>
+      <c r="J20">
+        <v>29</v>
+      </c>
+      <c r="K20">
+        <v>60</v>
+      </c>
+      <c r="L20">
+        <v>59</v>
+      </c>
+      <c r="M20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46296</v>
+      </c>
+      <c r="C21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F21">
+        <v>12060</v>
+      </c>
+      <c r="G21" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0.31319444444444444</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0.31319444444444444</v>
+      </c>
+      <c r="J21">
+        <v>59</v>
+      </c>
+      <c r="K21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" t="s">
+        <v>16</v>
+      </c>
+      <c r="M21" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
